--- a/synthetic/documents/xlsx/order_077_SW-01076.xlsx
+++ b/synthetic/documents/xlsx/order_077_SW-01076.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SafeWork Solutions Inc. (SYNTHETIC)</t>
+          <t>Nova Company (SYNTHETIC)</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Indianapolis Warehouse</t>
+          <t>Nova Shipping Location 1</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JAN-TWL-CF-BR</t>
+          <t>JAN-GCL-090</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Centerfeed Paper Towels Brown</t>
+          <t>Glass Cleaner RTU (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>42.27</v>
+        <v>38.55</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1014.48</v>
+        <v>192.75</v>
       </c>
     </row>
     <row r="10">
@@ -583,27 +583,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>STOR-TOTE-27</t>
+          <t>NOVA-JAN-3969</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Storage Tote 27 gallon with lid</t>
+          <t>Floor Stripper Heavy Duty (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.69</v>
+        <v>74.36</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>58.76</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="11">
@@ -612,16 +612,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JAN-LNR-3037-10-BL</t>
+          <t>PKG-STW-002</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Can Liner 30x37 1.0mil Black 250/CS</t>
+          <t>Stretch Wrap 18in (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>61.1</v>
+        <v>90.22</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>611</v>
+        <v>541.3200000000001</v>
       </c>
     </row>
     <row r="12">
@@ -641,27 +641,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>FST-HN-M81.25-ZN-B100</t>
+          <t>NOVA-PAC-0332</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Hex Nut M8-1.25 Grade 5 Zinc</t>
+          <t>Bubble Wrap 12in (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11.29</v>
+        <v>37.59</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>33.87</v>
+        <v>187.95</v>
       </c>
     </row>
     <row r="13">
@@ -670,16 +670,16 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JAN-GPC-RTU</t>
+          <t>NOVA-JAN-0113</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>General Purpose Cleaner ready to use 6/32 OZ</t>
+          <t>Disinfectant Spray (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>27.49</v>
+        <v>45.69</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>54.98</v>
+        <v>1096.56</v>
       </c>
     </row>
     <row r="14">
@@ -699,27 +699,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SWS-JS-2036</t>
+          <t>NOVA-FAS-6490</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Toilet Paper Dispenser Jumbo chrome</t>
+          <t>Flat Washer 3/4-10 Zinc (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>32.87</v>
+        <v>11.79</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>98.61</v>
+        <v>117.9</v>
       </c>
     </row>
     <row r="15">
@@ -728,27 +728,56 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SWS-MIS-3702</t>
+          <t>NOVA-JAN-3047</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Screwdriver Set Flat 5pc</t>
+          <t>Can Liner 33x39 1.2mil Clear (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>11.76</v>
+        <v>47.4</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>58.8</v>
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>JAN-DSP-185</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Disinfectant Spray (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>370.86</v>
       </c>
     </row>
   </sheetData>

--- a/synthetic/documents/xlsx/order_077_SW-01076.xlsx
+++ b/synthetic/documents/xlsx/order_077_SW-01076.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -511,88 +511,71 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Delivery Date:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>JAN-GCL-090</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Glass Cleaner RTU (SYNTHETIC)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>38.55</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>192.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>NOVA-JAN-3969</t>
+          <t>JAN-GCL-090</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Floor Stripper Heavy Duty (SYNTHETIC)</t>
+          <t>Glass Cleaner RTU (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -600,28 +583,28 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>74.36</v>
+        <v>38.55</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>74.36</v>
+        <v>192.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PKG-STW-002</t>
+          <t>NOVA-JAN-3969</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Stretch Wrap 18in (SYNTHETIC)</t>
+          <t>Floor Stripper Heavy Duty (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -629,154 +612,183 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>90.22</v>
+        <v>74.36</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>541.3200000000001</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>NOVA-PAC-0332</t>
+          <t>PKG-STW-002</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Bubble Wrap 12in (SYNTHETIC)</t>
+          <t>Stretch Wrap 18in (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>37.59</v>
+        <v>90.22</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>187.95</v>
+        <v>541.3200000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>NOVA-PAC-0332</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Bubble Wrap 12in (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>NOVA-JAN-0113</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Disinfectant Spray (SYNTHETIC)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>24</v>
-      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>45.69</v>
+        <v>37.59</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1096.56</v>
+        <v>187.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>NOVA-FAS-6490</t>
+          <t>NOVA-JAN-0113</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Flat Washer 3/4-10 Zinc (SYNTHETIC)</t>
+          <t>Disinfectant Spray (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>11.79</v>
+        <v>45.69</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>117.9</v>
+        <v>1096.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>NOVA-JAN-3047</t>
+          <t>NOVA-FAS-6490</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Can Liner 33x39 1.2mil Clear (SYNTHETIC)</t>
+          <t>Flat Washer 3/4-10 Zinc (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>47.4</v>
+        <v>11.79</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>47.4</v>
+        <v>117.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>NOVA-JAN-3047</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Can Liner 33x39 1.2mil Clear (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>JAN-DSP-185</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Disinfectant Spray (SYNTHETIC)</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D17" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>61.81</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>370.86</v>
       </c>
     </row>
